--- a/Testplan&TestDesign/20130271_TestDesign.xlsx
+++ b/Testplan&TestDesign/20130271_TestDesign.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\a\New folder\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eclipse1\SoftwareTesting_Nhom22_2024\Testplan&amp;TestDesign\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27825" windowHeight="12900"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="18330" windowHeight="6720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
   <si>
     <t>Table 1</t>
   </si>
@@ -163,6 +163,18 @@
   </si>
   <si>
     <t>Sử dụng bộ lọc trên trang kết quả và xác nhận bộ lọc hoạt động đúng theo các tiêu chí đã chọn</t>
+  </si>
+  <si>
+    <t>6.2 Thanh toán</t>
+  </si>
+  <si>
+    <t>Thanh toán giỏ hàng</t>
+  </si>
+  <si>
+    <t>Kiểm tra các chức năng liên quan đến thah toán</t>
+  </si>
+  <si>
+    <t>GUI+Function</t>
   </si>
 </sst>
 </file>
@@ -227,7 +239,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="21">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -236,236 +248,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color rgb="FF000000"/>
+      <left style="thin">
+        <color indexed="64"/>
       </left>
-      <right style="dotted">
-        <color rgb="FF000000"/>
+      <right style="thin">
+        <color indexed="64"/>
       </right>
-      <top/>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="dotted">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="dotted">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="dotted">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="dotted">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FFA5A5A5"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="dotted">
-        <color rgb="FF000000"/>
+      <top style="thin">
+        <color indexed="64"/>
       </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="dotted">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="dotted">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="dotted">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="dotted">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="dotted">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FFA5A5A5"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="dotted">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="dotted">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFA5A5A5"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FFA5A5A5"/>
+      <bottom style="thin">
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -473,110 +266,45 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -860,33 +588,34 @@
   <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="19.42578125" customWidth="1"/>
-    <col min="2" max="2" width="27.140625" customWidth="1"/>
-    <col min="3" max="3" width="45.7109375" customWidth="1"/>
-    <col min="4" max="4" width="52.5703125" customWidth="1"/>
-    <col min="6" max="6" width="9.7109375" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="96.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="52.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="5.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="27"/>
-      <c r="C1" s="27"/>
-      <c r="D1" s="27"/>
-      <c r="E1" s="27"/>
-      <c r="F1" s="27"/>
-      <c r="G1" s="27"/>
-    </row>
-    <row r="2" spans="1:7" ht="51.75" customHeight="1" thickBot="1">
-      <c r="A2" s="1" t="s">
+      <c r="B1" s="1"/>
+      <c r="C1" s="1"/>
+      <c r="D1" s="1"/>
+      <c r="E1" s="1"/>
+      <c r="F1" s="1"/>
+      <c r="G1" s="1"/>
+    </row>
+    <row r="2" spans="1:7" ht="25.5">
+      <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="2" t="s">
         <v>3</v>
       </c>
       <c r="D2" s="2" t="s">
@@ -898,269 +627,285 @@
       <c r="F2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="4"/>
-    </row>
-    <row r="3" spans="1:7" ht="43.5" customHeight="1" thickBot="1">
-      <c r="A3" s="5" t="s">
+      <c r="G2" s="3"/>
+    </row>
+    <row r="3" spans="1:7" ht="25.5">
+      <c r="A3" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="28" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
       <c r="C3" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="6" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="8"/>
-      <c r="G3" s="9"/>
-    </row>
-    <row r="4" spans="1:7" ht="64.5" customHeight="1" thickBot="1">
-      <c r="A4" s="10"/>
-      <c r="B4" s="29"/>
-      <c r="C4" s="11" t="s">
+      <c r="E3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+    </row>
+    <row r="4" spans="1:7" ht="25.5">
+      <c r="A4" s="8"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="8"/>
-      <c r="G4" s="9"/>
-    </row>
-    <row r="5" spans="1:7" ht="26.25" thickBot="1">
-      <c r="A5" s="10"/>
-      <c r="B5" s="29"/>
-      <c r="C5" s="12" t="s">
+      <c r="E4" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+    </row>
+    <row r="5" spans="1:7" ht="25.5">
+      <c r="A5" s="8"/>
+      <c r="B5" s="5"/>
+      <c r="C5" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="7" t="s">
+      <c r="D5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="7" t="s">
+      <c r="E5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="8"/>
-      <c r="G5" s="9"/>
-    </row>
-    <row r="6" spans="1:7" ht="39" thickBot="1">
-      <c r="A6" s="10"/>
-      <c r="B6" s="30"/>
-      <c r="C6" s="7" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+    </row>
+    <row r="6" spans="1:7" ht="25.5">
+      <c r="A6" s="8"/>
+      <c r="B6" s="5"/>
+      <c r="C6" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="8"/>
-      <c r="G6" s="9"/>
-    </row>
-    <row r="7" spans="1:7" ht="84" customHeight="1" thickBot="1">
-      <c r="A7" s="31"/>
-      <c r="B7" s="32" t="s">
+      <c r="E6" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="7"/>
+      <c r="G6" s="7"/>
+    </row>
+    <row r="7" spans="1:7" ht="25.5">
+      <c r="A7" s="9"/>
+      <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="13" t="s">
+      <c r="C7" s="11" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="D7" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="9"/>
-    </row>
-    <row r="8" spans="1:7" ht="71.25" customHeight="1" thickBot="1">
-      <c r="A8" s="31"/>
-      <c r="B8" s="33"/>
-      <c r="C8" s="14" t="s">
+      <c r="E7" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+    </row>
+    <row r="8" spans="1:7" ht="38.25">
+      <c r="A8" s="9"/>
+      <c r="B8" s="10"/>
+      <c r="C8" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="7" t="s">
+      <c r="D8" s="6" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="8"/>
-      <c r="G8" s="9"/>
-    </row>
-    <row r="9" spans="1:7" ht="39" thickBot="1">
-      <c r="A9" s="31"/>
-      <c r="B9" s="33"/>
-      <c r="C9" s="14" t="s">
+      <c r="E8" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+    </row>
+    <row r="9" spans="1:7" ht="25.5">
+      <c r="A9" s="9"/>
+      <c r="B9" s="10"/>
+      <c r="C9" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="7" t="s">
+      <c r="D9" s="6" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="7" t="s">
+      <c r="E9" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="8"/>
-      <c r="G9" s="9"/>
-    </row>
-    <row r="10" spans="1:7" ht="39" thickBot="1">
-      <c r="A10" s="31"/>
-      <c r="B10" s="33"/>
-      <c r="C10" s="14" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+    </row>
+    <row r="10" spans="1:7" ht="25.5">
+      <c r="A10" s="9"/>
+      <c r="B10" s="10"/>
+      <c r="C10" s="11" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="7" t="s">
+      <c r="D10" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="8"/>
-      <c r="G10" s="9"/>
-    </row>
-    <row r="11" spans="1:7" ht="51.75" thickBot="1">
-      <c r="A11" s="31"/>
-      <c r="B11" s="34"/>
-      <c r="C11" s="15" t="s">
+      <c r="E10" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+    </row>
+    <row r="11" spans="1:7" ht="25.5">
+      <c r="A11" s="9"/>
+      <c r="B11" s="10"/>
+      <c r="C11" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="7" t="s">
+      <c r="D11" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="8"/>
-      <c r="G11" s="9"/>
-    </row>
-    <row r="12" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A12" s="10"/>
-      <c r="B12" s="24" t="s">
+      <c r="E11" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+    </row>
+    <row r="12" spans="1:7">
+      <c r="A12" s="8"/>
+      <c r="B12" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="C12" s="22" t="s">
+      <c r="C12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="D12" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="7" t="s">
+      <c r="E12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="8"/>
-      <c r="G12" s="9"/>
-    </row>
-    <row r="13" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A13" s="10"/>
-      <c r="B13" s="25"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="7" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+    </row>
+    <row r="13" spans="1:7">
+      <c r="A13" s="8"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="10"/>
+      <c r="D13" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="8"/>
-      <c r="G13" s="9"/>
-    </row>
-    <row r="14" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A14" s="10"/>
-      <c r="B14" s="25"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="7" t="s">
+      <c r="E13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+    </row>
+    <row r="14" spans="1:7">
+      <c r="A14" s="8"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="10"/>
+      <c r="D14" s="6" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="8"/>
-      <c r="G14" s="9"/>
-    </row>
-    <row r="15" spans="1:7" ht="26.25" thickBot="1">
-      <c r="A15" s="10"/>
-      <c r="B15" s="25"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="7" t="s">
+      <c r="E14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+    </row>
+    <row r="15" spans="1:7" ht="25.5">
+      <c r="A15" s="8"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="10"/>
+      <c r="D15" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="7" t="s">
+      <c r="E15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="8"/>
-      <c r="G15" s="9"/>
-    </row>
-    <row r="16" spans="1:7" ht="39" thickBot="1">
-      <c r="A16" s="10"/>
-      <c r="B16" s="26"/>
-      <c r="C16" s="18" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+    </row>
+    <row r="16" spans="1:7" ht="25.5">
+      <c r="A16" s="8"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="11" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="7" t="s">
+      <c r="D16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="7" t="s">
+      <c r="E16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="8"/>
-      <c r="G16" s="9"/>
-    </row>
-    <row r="17" spans="1:7" ht="26.25" customHeight="1" thickBot="1">
-      <c r="A17" s="10"/>
-      <c r="B17" s="19" t="s">
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+    </row>
+    <row r="17" spans="1:7" ht="25.5">
+      <c r="A17" s="8"/>
+      <c r="B17" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="7" t="s">
+      <c r="D17" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="8"/>
-      <c r="G17" s="9"/>
-    </row>
-    <row r="18" spans="1:7" ht="39" thickBot="1">
-      <c r="A18" s="10"/>
-      <c r="B18" s="20"/>
-      <c r="C18" s="17" t="s">
+      <c r="E17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+    </row>
+    <row r="18" spans="1:7" ht="25.5">
+      <c r="A18" s="8"/>
+      <c r="B18" s="5"/>
+      <c r="C18" s="11" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="7" t="s">
+      <c r="D18" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="8"/>
-      <c r="G18" s="9"/>
-    </row>
-    <row r="19" spans="1:7" ht="39" thickBot="1">
-      <c r="A19" s="10"/>
-      <c r="B19" s="21"/>
-      <c r="C19" s="18" t="s">
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+    </row>
+    <row r="19" spans="1:7" ht="25.5">
+      <c r="A19" s="8"/>
+      <c r="B19" s="5"/>
+      <c r="C19" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="7" t="s">
+      <c r="D19" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="8"/>
-      <c r="G19" s="9"/>
+      <c r="E19" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="D20" s="7"/>
+      <c r="A20" s="8" t="s">
+        <v>45</v>
+      </c>
+      <c r="B20" s="13" t="s">
+        <v>46</v>
+      </c>
+      <c r="C20" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>47</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="F20" s="13"/>
+      <c r="G20" s="13"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/Testplan&TestDesign/20130271_TestDesign.xlsx
+++ b/Testplan&TestDesign/20130271_TestDesign.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>Table 1</t>
   </si>
@@ -163,18 +163,6 @@
   </si>
   <si>
     <t>Sử dụng bộ lọc trên trang kết quả và xác nhận bộ lọc hoạt động đúng theo các tiêu chí đã chọn</t>
-  </si>
-  <si>
-    <t>6.2 Thanh toán</t>
-  </si>
-  <si>
-    <t>Thanh toán giỏ hàng</t>
-  </si>
-  <si>
-    <t>Kiểm tra các chức năng liên quan đến thah toán</t>
-  </si>
-  <si>
-    <t>GUI+Function</t>
   </si>
 </sst>
 </file>
@@ -268,43 +256,43 @@
   </cellStyleXfs>
   <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -598,314 +586,304 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="12" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
-      <c r="E1" s="1"/>
-      <c r="F1" s="1"/>
-      <c r="G1" s="1"/>
+      <c r="B1" s="12"/>
+      <c r="C1" s="12"/>
+      <c r="D1" s="12"/>
+      <c r="E1" s="12"/>
+      <c r="F1" s="12"/>
+      <c r="G1" s="12"/>
     </row>
     <row r="2" spans="1:7" ht="25.5">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G2" s="3"/>
+      <c r="G2" s="2"/>
     </row>
     <row r="3" spans="1:7" ht="25.5">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="9" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F3" s="7"/>
-      <c r="G3" s="7"/>
+      <c r="E3" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="5"/>
+      <c r="G3" s="5"/>
     </row>
     <row r="4" spans="1:7" ht="25.5">
-      <c r="A4" s="8"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="7" t="s">
+      <c r="A4" s="6"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="E4" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F4" s="7"/>
-      <c r="G4" s="7"/>
+      <c r="E4" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="5"/>
+      <c r="G4" s="5"/>
     </row>
     <row r="5" spans="1:7" ht="25.5">
-      <c r="A5" s="8"/>
-      <c r="B5" s="5"/>
-      <c r="C5" s="7" t="s">
+      <c r="A5" s="6"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="7"/>
-      <c r="G5" s="7"/>
+      <c r="F5" s="5"/>
+      <c r="G5" s="5"/>
     </row>
     <row r="6" spans="1:7" ht="25.5">
-      <c r="A6" s="8"/>
-      <c r="B6" s="5"/>
-      <c r="C6" s="6" t="s">
+      <c r="A6" s="6"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="E6" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F6" s="7"/>
-      <c r="G6" s="7"/>
+      <c r="E6" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F6" s="5"/>
+      <c r="G6" s="5"/>
     </row>
     <row r="7" spans="1:7" ht="25.5">
-      <c r="A7" s="9"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="10" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="11" t="s">
+      <c r="C7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="4" t="s">
         <v>21</v>
       </c>
-      <c r="E7" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
+      <c r="E7" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F7" s="5"/>
+      <c r="G7" s="5"/>
     </row>
     <row r="8" spans="1:7" ht="38.25">
-      <c r="A8" s="9"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="10"/>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="4" t="s">
         <v>23</v>
       </c>
-      <c r="E8" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
+      <c r="E8" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F8" s="5"/>
+      <c r="G8" s="5"/>
     </row>
     <row r="9" spans="1:7" ht="25.5">
-      <c r="A9" s="9"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="10"/>
-      <c r="C9" s="11" t="s">
+      <c r="C9" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
+      <c r="F9" s="5"/>
+      <c r="G9" s="5"/>
     </row>
     <row r="10" spans="1:7" ht="25.5">
-      <c r="A10" s="9"/>
+      <c r="A10" s="13"/>
       <c r="B10" s="10"/>
-      <c r="C10" s="11" t="s">
+      <c r="C10" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="E10" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
+      <c r="E10" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5"/>
     </row>
     <row r="11" spans="1:7" ht="25.5">
-      <c r="A11" s="9"/>
+      <c r="A11" s="13"/>
       <c r="B11" s="10"/>
-      <c r="C11" s="11" t="s">
+      <c r="C11" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E11" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
+      <c r="E11" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F11" s="5"/>
+      <c r="G11" s="5"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="8"/>
-      <c r="B12" s="12" t="s">
+      <c r="A12" s="6"/>
+      <c r="B12" s="11" t="s">
         <v>37</v>
       </c>
       <c r="C12" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D12" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="E12" s="6" t="s">
+      <c r="E12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
+      <c r="F12" s="5"/>
+      <c r="G12" s="5"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="8"/>
-      <c r="B13" s="12"/>
+      <c r="A13" s="6"/>
+      <c r="B13" s="11"/>
       <c r="C13" s="10"/>
-      <c r="D13" s="6" t="s">
+      <c r="D13" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="E13" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
+      <c r="E13" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="8"/>
-      <c r="B14" s="12"/>
+      <c r="A14" s="6"/>
+      <c r="B14" s="11"/>
       <c r="C14" s="10"/>
-      <c r="D14" s="6" t="s">
+      <c r="D14" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="E14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
+      <c r="E14" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F14" s="5"/>
+      <c r="G14" s="5"/>
     </row>
     <row r="15" spans="1:7" ht="25.5">
-      <c r="A15" s="8"/>
-      <c r="B15" s="12"/>
+      <c r="A15" s="6"/>
+      <c r="B15" s="11"/>
       <c r="C15" s="10"/>
-      <c r="D15" s="6" t="s">
+      <c r="D15" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="E15" s="6" t="s">
+      <c r="E15" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
+      <c r="F15" s="5"/>
+      <c r="G15" s="5"/>
     </row>
     <row r="16" spans="1:7" ht="25.5">
-      <c r="A16" s="8"/>
-      <c r="B16" s="12"/>
-      <c r="C16" s="11" t="s">
+      <c r="A16" s="6"/>
+      <c r="B16" s="11"/>
+      <c r="C16" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="D16" s="6" t="s">
+      <c r="D16" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E16" s="6" t="s">
+      <c r="E16" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
+      <c r="F16" s="5"/>
+      <c r="G16" s="5"/>
     </row>
     <row r="17" spans="1:7" ht="25.5">
-      <c r="A17" s="8"/>
-      <c r="B17" s="5" t="s">
+      <c r="A17" s="6"/>
+      <c r="B17" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="11" t="s">
+      <c r="C17" s="7" t="s">
         <v>39</v>
       </c>
-      <c r="D17" s="6" t="s">
+      <c r="D17" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="E17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
+      <c r="E17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F17" s="5"/>
+      <c r="G17" s="5"/>
     </row>
     <row r="18" spans="1:7" ht="25.5">
-      <c r="A18" s="8"/>
-      <c r="B18" s="5"/>
-      <c r="C18" s="11" t="s">
+      <c r="A18" s="6"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="7" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="6" t="s">
+      <c r="D18" s="4" t="s">
         <v>42</v>
       </c>
-      <c r="E18" s="6" t="s">
+      <c r="E18" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
+      <c r="F18" s="5"/>
+      <c r="G18" s="5"/>
     </row>
     <row r="19" spans="1:7" ht="25.5">
-      <c r="A19" s="8"/>
-      <c r="B19" s="5"/>
-      <c r="C19" s="11" t="s">
+      <c r="A19" s="6"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="D19" s="6" t="s">
+      <c r="D19" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E19" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
+      <c r="E19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="F19" s="5"/>
+      <c r="G19" s="5"/>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="8" t="s">
-        <v>45</v>
-      </c>
-      <c r="B20" s="13" t="s">
-        <v>46</v>
-      </c>
-      <c r="C20" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>47</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>48</v>
-      </c>
-      <c r="F20" s="13"/>
-      <c r="G20" s="13"/>
+      <c r="A20" s="6"/>
+      <c r="B20" s="8"/>
+      <c r="C20" s="8"/>
+      <c r="D20" s="8"/>
+      <c r="E20" s="8"/>
+      <c r="F20" s="8"/>
+      <c r="G20" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="7">
